--- a/Xlsx/Activity/ActivityType.xlsx
+++ b/Xlsx/Activity/ActivityType.xlsx
@@ -47,7 +47,7 @@
     <t>Quest</t>
   </si>
   <si>
-    <t>string</t>
+    <t>String</t>
   </si>
   <si>
     <t>活动类型</t>
